--- a/src/Excelsior.Tests/TypeInferenceTests.DataBoundInfersWhenEnabled.verified.xlsx
+++ b/src/Excelsior.Tests/TypeInferenceTests.DataBoundInfersWhenEnabled.verified.xlsx
@@ -146,10 +146,10 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation type="custom" allowBlank="0" showErrorMessage="1" sqref="C2:C7">
+    <dataValidation type="custom" allowBlank="0" showErrorMessage="1" errorTitle="Invalid value" error="Must be a number." sqref="C2:C7">
       <formula1>ISNUMBER(C2)</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="0" showErrorMessage="1" sqref="E2:E7">
+    <dataValidation type="list" allowBlank="0" showErrorMessage="1" errorTitle="Invalid value" error="Must be one of: TRUE, FALSE." sqref="E2:E7">
       <formula1>"TRUE,FALSE"</formula1>
     </dataValidation>
   </dataValidations>

--- a/src/Excelsior.Tests/TypeInferenceTests.DataBoundInfersWhenEnabled.verified.xlsx
+++ b/src/Excelsior.Tests/TypeInferenceTests.DataBoundInfersWhenEnabled.verified.xlsx
@@ -145,13 +145,19 @@
       <formula>LEN(TRIM(F2))=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="2">
+  <dataValidations count="4">
+    <dataValidation type="custom" allowBlank="0" showErrorMessage="1" errorTitle="Invalid value" error="This field is required." sqref="A2:A7">
+      <formula1>LEN(TRIM(A2))&gt;0</formula1>
+    </dataValidation>
     <dataValidation type="custom" allowBlank="0" showErrorMessage="1" errorTitle="Invalid value" error="Must be a number." sqref="C2:C7">
       <formula1>ISNUMBER(C2)</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="0" showErrorMessage="1" errorTitle="Invalid value" error="Must be one of: TRUE, FALSE." sqref="E2:E7">
       <formula1>"TRUE,FALSE"</formula1>
     </dataValidation>
+    <dataValidation type="custom" allowBlank="0" showErrorMessage="1" errorTitle="Invalid value" error="This field is required." sqref="F2:F7">
+      <formula1>LEN(TRIM(F2))&gt;0</formula1>
+    </dataValidation>
   </dataValidations>
 </worksheet>
 </file>
--- a/src/Excelsior.Tests/TypeInferenceTests.DataBoundInfersWhenEnabled.verified.xlsx
+++ b/src/Excelsior.Tests/TypeInferenceTests.DataBoundInfersWhenEnabled.verified.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="DeterministicId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="DeterministicId3"/>
   </sheets>
 </workbook>
 </file>
@@ -160,4 +160,17 @@
     </dataValidation>
   </dataValidations>
 </worksheet>
+</file>
+
+<file path=customXml/item.xml><?xml version="1.0" encoding="utf-8"?>
+<columnMetadata xmlns="https://github.com/SimonCropp/Excelsior/columnMetadata/v1">
+  <sheet name="Sheet1">
+    <column index="1" property="Name"/>
+    <column index="2" property="Notes"/>
+    <column index="3" property="Age"/>
+    <column index="4" property="Score"/>
+    <column index="5" property="IsActive"/>
+    <column index="6" property="HireDate"/>
+  </sheet>
+</columnMetadata>
 </file>
--- a/src/Excelsior.Tests/TypeInferenceTests.DataBoundInfersWhenEnabled.verified.xlsx
+++ b/src/Excelsior.Tests/TypeInferenceTests.DataBoundInfersWhenEnabled.verified.xlsx
@@ -117,7 +117,7 @@
       </c>
       <c r="D2" s="2"/>
       <c r="E2" s="2" t="b">
-        <v>true</v>
+        <v>1</v>
       </c>
       <c r="F2" s="3">
         <v>43831</v>

--- a/src/Excelsior.Tests/TypeInferenceTests.DataBoundInfersWhenEnabled.verified.xlsx
+++ b/src/Excelsior.Tests/TypeInferenceTests.DataBoundInfersWhenEnabled.verified.xlsx
@@ -70,7 +70,7 @@
     <col min="3" max="3" width="9" customWidth="1"/>
     <col min="4" max="4" width="9" customWidth="1"/>
     <col min="5" max="5" width="13" customWidth="1"/>
-    <col min="6" max="6" width="13" customWidth="1"/>
+    <col min="6" max="6" width="24" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
